--- a/data/flux/paper_code_data/source_data/Fig1_sites_and_EFPs.xlsx
+++ b/data/flux/paper_code_data/source_data/Fig1_sites_and_EFPs.xlsx
@@ -54,7 +54,7 @@
     <t>last_year</t>
   </si>
   <si>
-    <t>total_mortality_site_max_pct</t>
+    <t>relative_mortality_site_max_pct</t>
   </si>
   <si>
     <t>mortality_class</t>
